--- a/downloads/daily/b03-paste-values.xlsx
+++ b/downloads/daily/b03-paste-values.xlsx
@@ -591,7 +591,7 @@
         <v>5000</v>
       </c>
       <c r="C5" s="6">
-        <f>A2*B2</f>
+        <f>A5*B5</f>
         <v/>
       </c>
     </row>
@@ -603,7 +603,7 @@
         <v>12000</v>
       </c>
       <c r="C6" s="6">
-        <f>A3*B3</f>
+        <f>A6*B6</f>
         <v/>
       </c>
     </row>
@@ -615,7 +615,7 @@
         <v>8000</v>
       </c>
       <c r="C7" s="6">
-        <f>A4*B4</f>
+        <f>A7*B7</f>
         <v/>
       </c>
     </row>
